--- a/results/job_matches_2026-07-26.xlsx
+++ b/results/job_matches_2026-07-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inadev Corporation</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,42 +486,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Azure, Databricks, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81a4ee6ef1c78d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2cc185aab9474c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Data Architect</t>
+          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Azure, Databricks, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2cc185aab9474c</t>
+          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
+          <t>DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>Unlimited Systems</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
+          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer- Analytics Products</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gradera</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TAIT</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
+          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Hybrid)</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unlimited Systems</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Backend Python Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -775,391 +775,6 @@
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Cargill</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Liquidity Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Mulesoft Developer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Centurion Consulting Group</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Java Developer with AI Experience</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Glint Tech Solutions</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Versa Networks</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Abbott</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Alameda, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Backend Python Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>California City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>

--- a/results/job_matches_2026-07-26.xlsx
+++ b/results/job_matches_2026-07-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unlimited Systems</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,215 +566,75 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
+          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Python Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Mulesoft Developer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Centurion Consulting Group</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Java Developer with AI Experience</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Glint Tech Solutions</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Abbott</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Alameda, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Backend Python Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>California City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>

--- a/results/job_matches_2026-07-26.xlsx
+++ b/results/job_matches_2026-07-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,75 +566,40 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
+          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mulesoft Developer</t>
+          <t>Backend Python Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Backend Python Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>California City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>

--- a/results/job_matches_2026-07-26.xlsx
+++ b/results/job_matches_2026-07-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,103 +503,173 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Software Engineer - Egypt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Egypt, AR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
+          <t>https://www.indeed.com/viewjob?jk=a89355d34c2e7d21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mulesoft Developer</t>
+          <t>Senior QA Engineer - Egypt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Egypt, AR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb073c25dabf3264</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cargill</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mulesoft Developer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Centurion Consulting Group</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Backend Python Engineer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>California City, CA, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D7" t="n">
         <v>10.4</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>

--- a/results/job_matches_2026-07-26.xlsx
+++ b/results/job_matches_2026-07-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,77 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mulesoft Developer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Centurion Consulting Group</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Backend Python Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>California City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-26.xlsx
+++ b/results/job_matches_2026-07-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,33 +573,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Sr Java Enterprise Architect in Irvine, CA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ValueBase Consulting</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf9f970e709cc18a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Mulesoft Developer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Centurion Consulting Group</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>McLean, VA, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>11.1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
         </is>

--- a/results/job_matches_2026-07-26.xlsx
+++ b/results/job_matches_2026-07-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,41 +602,6 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cf9f970e709cc18a</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mulesoft Developer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Centurion Consulting Group</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-26.xlsx
+++ b/results/job_matches_2026-07-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,6 +602,41 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cf9f970e709cc18a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-26.xlsx
+++ b/results/job_matches_2026-07-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,33 +608,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>True Religion Brand Jeans</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d25577e9f3e1876</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>American Airlines</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>11.8</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
         </is>
